--- a/plantillas_excel/25_valorizacion_pkg.xlsx
+++ b/plantillas_excel/25_valorizacion_pkg.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -682,6 +682,26 @@
           <t>ESTADO</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PCM REF</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>DIAS OP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -744,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:BI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -837,6 +857,231 @@
       <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Hoja de salida — la completa el script. No hace falta escribir nada acá.</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>FECHA ANT</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>FECHA NUEVA</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>MARKUP JSON</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>PRICE CODE</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>1+0</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2+0</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>3+0</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>4+0</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>5+0</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>6+0</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>7+0</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>8+0</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>9+0</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>10+0</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>11+0</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>12+0</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>13+0</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>14+0</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>15+0</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>16+0</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>17+0</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>18+0</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>19+0</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>20+0</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>21+0</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>22+0</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>23+0</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>24+0</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>25+0</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>26+0</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>27+0</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>28+0</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>29+0</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>30+0</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>31+0</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>32+0</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>33+0</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>34+0</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>35+0</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>36+0</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>37+0</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>38+0</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>39+0</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>40+0</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>41+0</t>
         </is>
       </c>
     </row>
